--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484113_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484113_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S. HALL</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.025</v>
+        <v>4.5753</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9624</v>
+        <v>3.9904</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0625</v>
+        <v>0.5849</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6791</v>
+        <v>0.7302</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2046</v>
+        <v>0.3778</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4745</v>
+        <v>0.3524</v>
       </c>
       <c r="J2" t="n">
-        <v>5.2627</v>
+        <v>1.0337</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8078</v>
+        <v>0.4287</v>
       </c>
       <c r="L2" t="n">
-        <v>2.455</v>
+        <v>0.605</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.5837</v>
+        <v>-0.3035</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6032</v>
+        <v>-0.0509</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0195</v>
+        <v>-0.2526</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7855</v>
+        <v>1.1903</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2904</v>
+        <v>-0.0241</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3581</v>
+        <v>0.2778</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9323</v>
+        <v>-0.3019</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.7461</v>
+        <v>2.6789</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.6745</v>
+        <v>2.6789</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0716</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9668</v>
+        <v>3.9286</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1</v>
+        <v>2.9777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8668</v>
+        <v>0.951</v>
       </c>
       <c r="G3" t="n">
         <v>3.7848</v>
@@ -688,13 +688,13 @@
         <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8756</v>
+        <v>0.8375</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9726</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.097</v>
+        <v>-0.0129</v>
       </c>
       <c r="V3" t="n">
         <v>2.6789</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. LORAS MONTERO</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.823</v>
+        <v>3.6144</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6085</v>
+        <v>3.8016</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2145</v>
+        <v>-0.1872</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0749</v>
+        <v>-3.0896</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.9729</v>
+        <v>-0.8366</v>
       </c>
       <c r="I4" t="n">
-        <v>1.898</v>
+        <v>-2.253</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2366</v>
+        <v>-0.3288</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2961</v>
+        <v>1.024</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5327</v>
+        <v>-1.3527</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3115</v>
+        <v>-2.7608</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.6768</v>
+        <v>-1.8606</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6347</v>
+        <v>-0.9003</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1822</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1822</v>
+        <v>2.7774</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2552</v>
+        <v>0.8701</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0463</v>
+        <v>0.4706</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2089</v>
+        <v>0.3995</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5396</v>
+        <v>6.0323</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6745</v>
+        <v>6.6355</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1349</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>S. HALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5525</v>
+        <v>3.4818</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2762</v>
+        <v>3.8401</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2763</v>
+        <v>-0.3583</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7302</v>
+        <v>3.6791</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3778</v>
+        <v>1.2046</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3524</v>
+        <v>2.4745</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0337</v>
+        <v>5.2627</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4287</v>
+        <v>2.8078</v>
       </c>
       <c r="L5" t="n">
-        <v>0.605</v>
+        <v>2.455</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3035</v>
+        <v>-1.5837</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0509</v>
+        <v>-1.6032</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2526</v>
+        <v>0.0195</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1903</v>
+        <v>1.7855</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0469</v>
+        <v>1.7472</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4364</v>
+        <v>1.2357</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6105</v>
+        <v>0.5115</v>
       </c>
       <c r="V5" t="n">
-        <v>2.6789</v>
+        <v>-1.7461</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6789</v>
+        <v>-0.6745</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0716</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>D. LORAS MONTERO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3952</v>
+        <v>2.7798</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0874</v>
+        <v>3.0983</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6922</v>
+        <v>-0.3186</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.0896</v>
+        <v>-1.0749</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8366</v>
+        <v>-2.9729</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.253</v>
+        <v>1.898</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3288</v>
+        <v>2.2366</v>
       </c>
       <c r="K6" t="n">
-        <v>1.024</v>
+        <v>-0.2961</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3527</v>
+        <v>2.5327</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7608</v>
+        <v>-3.3115</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8606</v>
+        <v>-2.6768</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9003</v>
+        <v>-0.6347</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1984</v>
+        <v>2.1822</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7774</v>
+        <v>2.1822</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3491</v>
+        <v>2.212</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2436</v>
+        <v>1.5362</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1055</v>
+        <v>0.6758</v>
       </c>
       <c r="V6" t="n">
-        <v>6.0323</v>
+        <v>-0.5396</v>
       </c>
       <c r="W6" t="n">
-        <v>6.6355</v>
+        <v>-0.6745</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6032</v>
+        <v>0.1349</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1852</v>
+        <v>1.2974</v>
       </c>
       <c r="E7" t="n">
         <v>0.6362</v>
       </c>
       <c r="F7" t="n">
-        <v>0.549</v>
+        <v>0.6612</v>
       </c>
       <c r="G7" t="n">
         <v>0.2216</v>
@@ -1000,13 +1000,13 @@
         <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6303</v>
+        <v>0.7425</v>
       </c>
       <c r="T7" t="n">
         <v>0.5555</v>
       </c>
       <c r="U7" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="V7" t="n">
         <v>0.1349</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7124</v>
+        <v>0.8157</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0606</v>
+        <v>0.7421</v>
       </c>
       <c r="F8" t="n">
-        <v>0.773</v>
+        <v>0.0736</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4046</v>
+        <v>0.3365</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6702</v>
+        <v>-0.1766</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2656</v>
+        <v>0.513</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0149</v>
+        <v>0.6627</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.0149</v>
+        <v>0.0202</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4195</v>
+        <v>-0.3263</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6851</v>
+        <v>-0.1967</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2656</v>
+        <v>-0.1295</v>
       </c>
       <c r="P8" t="n">
         <v>0.3968</v>
@@ -1078,28 +1078,28 @@
         <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.089</v>
+        <v>-0.0524</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3117</v>
+        <v>0.0794</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2227</v>
+        <v>-0.1318</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.1349</v>
       </c>
       <c r="W8" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.266</v>
+        <v>0.1349</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5275</v>
+        <v>0.5619</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5381</v>
+        <v>0.0414</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0106</v>
+        <v>0.5205</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3365</v>
+        <v>0.4046</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1766</v>
+        <v>0.6702</v>
       </c>
       <c r="I9" t="n">
-        <v>0.513</v>
+        <v>-0.2656</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6627</v>
+        <v>-0.0149</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0202</v>
+        <v>-0.0149</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6425999999999999</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3263</v>
+        <v>0.4195</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1967</v>
+        <v>0.6851</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1295</v>
+        <v>-0.2656</v>
       </c>
       <c r="P9" t="n">
         <v>0.3968</v>
@@ -1156,22 +1156,22 @@
         <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3407</v>
+        <v>-0.2395</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1247</v>
+        <v>-0.2097</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.216</v>
+        <v>-0.0298</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1349</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1349</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0224</v>
+        <v>-0.928</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1474</v>
+        <v>-0.2494</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8749</v>
+        <v>-0.6786</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5901999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1071</v>
+        <v>-0.0127</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3061</v>
+        <v>0.2041</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4132</v>
+        <v>-0.2168</v>
       </c>
       <c r="V10" t="n">
         <v>0.6669</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3154</v>
+        <v>-2.0093</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.505</v>
+        <v>-1.1989</v>
       </c>
       <c r="F11" t="n">
         <v>-0.8104</v>
@@ -1312,10 +1312,10 @@
         <v>1.7855</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6575</v>
+        <v>0.9636</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7483</v>
+        <v>1.0544</v>
       </c>
       <c r="U11" t="n">
         <v>-0.09080000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0593</v>
+        <v>-2.3273</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2661</v>
+        <v>-2.4499</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2068</v>
+        <v>0.1226</v>
       </c>
       <c r="G12" t="n">
         <v>-2.8473</v>
@@ -1390,13 +1390,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1525</v>
+        <v>0.5796</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5498</v>
+        <v>0.2665</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3973</v>
+        <v>0.3131</v>
       </c>
       <c r="V12" t="n">
         <v>0.3373</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.7905</v>
+        <v>15.7903</v>
       </c>
       <c r="E13" t="n">
-        <v>15.2297</v>
+        <v>15.2296</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5607999999999999</v>
+        <v>0.5607</v>
       </c>
       <c r="G13" t="n">
         <v>0.7127000000000008</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6801999999999997</v>
+        <v>0.6802000000000006</v>
       </c>
       <c r="I13" t="n">
-        <v>0.03239999999999954</v>
+        <v>0.0323999999999991</v>
       </c>
       <c r="J13" t="n">
         <v>13.4599</v>
@@ -1456,7 +1456,7 @@
         <v>-9.6065</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.140899999999999</v>
+        <v>-3.1409</v>
       </c>
       <c r="P13" t="n">
         <v>-1.9838</v>
@@ -1468,13 +1468,13 @@
         <v>14.879</v>
       </c>
       <c r="S13" t="n">
-        <v>7.623699999999999</v>
+        <v>7.623800000000002</v>
       </c>
       <c r="T13" t="n">
-        <v>6.3207</v>
+        <v>6.3208</v>
       </c>
       <c r="U13" t="n">
-        <v>1.303</v>
+        <v>1.3029</v>
       </c>
       <c r="V13" t="n">
         <v>9.437900000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0364</v>
+        <v>2.4413</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7947</v>
+        <v>2.3866</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2417</v>
+        <v>0.0547</v>
       </c>
       <c r="G14" t="n">
         <v>2.1145</v>
@@ -1546,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1166</v>
+        <v>0.5215</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6802</v>
+        <v>0.2721</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4364</v>
+        <v>0.2494</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1947</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. SERRATACO SANCHEZ</t>
+          <t>A. CRUZ URBANEJA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0141</v>
+        <v>0.2545</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3501</v>
+        <v>3.2707</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3642</v>
+        <v>-3.0163</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.7517</v>
+        <v>2.794</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.4033</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3485</v>
+        <v>1.872</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.3729</v>
+        <v>3.5663</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.4131</v>
+        <v>1.7137</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0402</v>
+        <v>1.8525</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3788</v>
+        <v>-0.7723</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0098</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3886</v>
+        <v>0.0195</v>
       </c>
       <c r="P15" t="n">
         <v>0.9919</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2419</v>
+        <v>-1.7217</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4908</v>
+        <v>-0.5101</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2489</v>
+        <v>-1.2116</v>
       </c>
       <c r="V15" t="n">
-        <v>0.532</v>
+        <v>-1.8097</v>
       </c>
       <c r="W15" t="n">
-        <v>0.532</v>
+        <v>1.2065</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. CRUZ URBANEJA</t>
+          <t>. VICENTE SABARIEGO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,75 +1657,71 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2361</v>
+        <v>-0.0926</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1687</v>
+        <v>-0.2302</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.4048</v>
+        <v>0.1376</v>
       </c>
       <c r="G16" t="n">
-        <v>2.794</v>
+        <v>-0.9726</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9219000000000001</v>
+        <v>-0.4389</v>
       </c>
       <c r="I16" t="n">
-        <v>1.872</v>
+        <v>-0.5337</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5663</v>
+        <v>0.3423</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7137</v>
+        <v>0.2218</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8525</v>
+        <v>0.1205</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7723</v>
+        <v>-1.3148</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.6607</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0195</v>
+        <v>-0.6542</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.2123</v>
+        <v>-1.1039</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6121</v>
+        <v>-0.5724</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.6002</v>
+        <v>-0.5314</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8097</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>. VICENTE SABARIEGO</t>
-        </is>
-      </c>
+      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1735,13 +1731,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4471</v>
+        <v>-0.0926</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3322</v>
+        <v>-0.2302</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1149</v>
+        <v>0.1376</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9726</v>
@@ -1780,13 +1776,13 @@
         <v>1.9838</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4584</v>
+        <v>-1.1039</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6744</v>
+        <v>-0.5724</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7839</v>
+        <v>-0.5314</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1799,7 +1795,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P. MULIO CAMPOS</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>TIBU-RON CASTELLDEFELS</t>
@@ -1809,58 +1809,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4471</v>
+        <v>-0.249</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3322</v>
+        <v>-0.4296</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1149</v>
+        <v>0.1806</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9726</v>
+        <v>-0.9916</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4389</v>
+        <v>-0.4941</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5337</v>
+        <v>-0.4975</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3423</v>
+        <v>-0.5997</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2218</v>
+        <v>0.0403</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1205</v>
+        <v>-0.64</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3148</v>
+        <v>-0.3918</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6607</v>
+        <v>-0.5344</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6542</v>
+        <v>0.1425</v>
       </c>
       <c r="P18" t="n">
-        <v>1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4584</v>
+        <v>0.3458</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6744</v>
+        <v>0.1701</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7839</v>
+        <v>0.1757</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1887,13 +1887,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6206</v>
+        <v>-0.6283</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7082</v>
+        <v>2.5041</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3288</v>
+        <v>-3.1324</v>
       </c>
       <c r="G19" t="n">
         <v>2.0735</v>
@@ -1932,13 +1932,13 @@
         <v>1.9838</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.099</v>
+        <v>-1.1067</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1813</v>
+        <v>-0.3853</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9177</v>
+        <v>-0.7214</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6032</v>
@@ -1953,7 +1953,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MULIO CAMPOS</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1965,73 +1965,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6571</v>
+        <v>-0.9101</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8377</v>
+        <v>-0.022</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1806</v>
+        <v>-0.888</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9916</v>
+        <v>-0.0253</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4941</v>
+        <v>-0.0253</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4975</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5997</v>
+        <v>0.0403</v>
       </c>
       <c r="K20" t="n">
         <v>0.0403</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.64</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3918</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5344</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1425</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
+        <v>-0.0156</v>
+      </c>
+      <c r="T20" t="n">
         <v>-0.0623</v>
       </c>
-      <c r="T20" t="n">
-        <v>-0.238</v>
-      </c>
       <c r="U20" t="n">
-        <v>0.1757</v>
+        <v>0.0468</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>S. SERRATACO SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2043,67 +2043,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9381</v>
+        <v>-1.1584</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.022</v>
+        <v>-1.5745</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9161</v>
+        <v>0.4161</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0253</v>
+        <v>-2.7517</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0253</v>
+        <v>-2.4033</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.3485</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0403</v>
+        <v>-2.3729</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0403</v>
+        <v>-2.4131</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.3788</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.0098</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.3886</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0436</v>
+        <v>0.06950000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0623</v>
+        <v>0.2665</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0187</v>
+        <v>-0.197</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.8692</v>
+        <v>0.532</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2121,13 +2121,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6602</v>
+        <v>-2.1312</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.556</v>
+        <v>-0.6581</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1042</v>
+        <v>-1.4731</v>
       </c>
       <c r="G22" t="n">
         <v>-0.383</v>
@@ -2166,13 +2166,13 @@
         <v>2.579</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6145</v>
+        <v>-1.0855</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1076</v>
+        <v>-0.2096</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5069</v>
+        <v>-0.8759</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2199,13 +2199,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1262</v>
+        <v>-2.1441</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9728</v>
+        <v>-1.0748</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1534</v>
+        <v>-1.0692</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5451</v>
@@ -2244,13 +2244,13 @@
         <v>2.9758</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0492</v>
+        <v>-1.067</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2323</v>
+        <v>-0.3343</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8169</v>
+        <v>-0.7327</v>
       </c>
       <c r="V23" t="n">
         <v>-0.532</v>
@@ -2265,7 +2265,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. GASSAMA KARGBO</t>
+          <t>J. ARNAL DIAZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2277,73 +2277,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.0633</v>
+        <v>-2.2949</v>
       </c>
       <c r="E24" t="n">
-        <v>1.1803</v>
+        <v>-1.8341</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2436</v>
+        <v>-0.4608</v>
       </c>
       <c r="G24" t="n">
-        <v>1.4395</v>
+        <v>0.0616</v>
       </c>
       <c r="H24" t="n">
-        <v>1.4822</v>
+        <v>1.1394</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0427</v>
+        <v>-1.0779</v>
       </c>
       <c r="J24" t="n">
-        <v>1.22</v>
+        <v>1.1699</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1396</v>
+        <v>1.7296</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0803</v>
+        <v>-0.5597</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2195</v>
+        <v>-1.1083</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3425</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.123</v>
+        <v>-0.5182</v>
       </c>
       <c r="P24" t="n">
-        <v>0.5952</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5952</v>
+        <v>1.5871</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2721</v>
+        <v>-0.9678</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0396</v>
+        <v>-0.0283</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2324</v>
+        <v>-0.9396</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.8259</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.8259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. ARNAL DIAZ</t>
+          <t>B. GASSAMA KARGBO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2355,67 +2355,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.1936</v>
+        <v>-2.6552</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.3442</v>
+        <v>1.5884</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8494</v>
+        <v>-4.2436</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0616</v>
+        <v>1.4395</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1394</v>
+        <v>1.4822</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0779</v>
+        <v>-0.0427</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1699</v>
+        <v>1.22</v>
       </c>
       <c r="K25" t="n">
-        <v>1.7296</v>
+        <v>1.1396</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5597</v>
+        <v>0.0803</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1083</v>
+        <v>0.2195</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.5901999999999999</v>
+        <v>0.3425</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.5182</v>
+        <v>-0.123</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.3887</v>
+        <v>0.5952</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5871</v>
+        <v>0.5952</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.8665</v>
+        <v>0.136</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5384</v>
+        <v>0.3685</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.3281</v>
+        <v>-0.2324</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-4.8259</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-4.8259</v>
       </c>
     </row>
     <row r="26">
@@ -2433,13 +2433,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.8985</v>
+        <v>-5.3467</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.9976</v>
+        <v>-4.3855</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9008</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-3.5266</v>
@@ -2478,13 +2478,13 @@
         <v>1.7855</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3043</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.1756</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5165</v>
+        <v>-0.5768</v>
       </c>
       <c r="V26" t="n">
         <v>-0.8692</v>
@@ -2511,13 +2511,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-16.2374</v>
+        <v>-15.0073</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.8929</v>
+        <v>-0.6891999999999996</v>
       </c>
       <c r="F27" t="n">
-        <v>-15.3444</v>
+        <v>-14.318</v>
       </c>
       <c r="G27" t="n">
         <v>-1.6854</v>
@@ -2556,13 +2556,13 @@
         <v>18.8465</v>
       </c>
       <c r="S27" t="n">
-        <v>-9.082100000000001</v>
+        <v>-7.851800000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.9772</v>
+        <v>-1.7731</v>
       </c>
       <c r="U27" t="n">
-        <v>-7.1046</v>
+        <v>-6.0783</v>
       </c>
       <c r="V27" t="n">
         <v>-9.437899999999999</v>
